--- a/backend/data/financials_by_company/0197.HK.xlsx
+++ b/backend/data/financials_by_company/0197.HK.xlsx
@@ -662,580 +662,580 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-138913.202636</v>
+        <v>-410514.606229</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00122</v>
+        <v>0.011646</v>
       </c>
       <c r="D2" t="n">
-        <v>-39890000</v>
+        <v>-161680000</v>
       </c>
       <c r="E2" t="n">
-        <v>-113844000</v>
+        <v>-35250000</v>
       </c>
       <c r="F2" t="n">
-        <v>-113844000</v>
+        <v>-35250000</v>
       </c>
       <c r="G2" t="n">
-        <v>-196448000</v>
+        <v>-247213000</v>
       </c>
       <c r="H2" t="n">
-        <v>42628000</v>
+        <v>52751000</v>
       </c>
       <c r="I2" t="n">
-        <v>405318000</v>
+        <v>502746000</v>
       </c>
       <c r="J2" t="n">
-        <v>-153734000</v>
+        <v>-196930000</v>
       </c>
       <c r="K2" t="n">
-        <v>-196362000</v>
+        <v>-249681000</v>
       </c>
       <c r="L2" t="n">
-        <v>6285000</v>
+        <v>13082000</v>
       </c>
       <c r="M2" t="n">
-        <v>326000</v>
+        <v>452000</v>
       </c>
       <c r="N2" t="n">
-        <v>6611000</v>
+        <v>13534000</v>
       </c>
       <c r="O2" t="n">
-        <v>-82742913.202636</v>
+        <v>-212373514.606229</v>
       </c>
       <c r="P2" t="n">
-        <v>-196448000</v>
+        <v>-247213000</v>
       </c>
       <c r="Q2" t="n">
-        <v>531478000</v>
+        <v>753840000</v>
       </c>
       <c r="R2" t="n">
-        <v>-196362000</v>
+        <v>-249681000</v>
       </c>
       <c r="S2" t="n">
-        <v>112809468</v>
+        <v>93634809</v>
       </c>
       <c r="T2" t="n">
-        <v>112809468</v>
+        <v>93634809</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.74</v>
+        <v>-2.6</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.74</v>
+        <v>-2.6</v>
       </c>
       <c r="W2" t="n">
-        <v>-196448000</v>
+        <v>-247213000</v>
       </c>
       <c r="X2" t="n">
-        <v>-196448000</v>
+        <v>-247213000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-196448000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+        <v>-247213000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>7000</v>
+      </c>
       <c r="AB2" t="n">
-        <v>-196448000</v>
+        <v>-247220000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-196448000</v>
+        <v>-247220000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-240000</v>
+        <v>-2913000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-196688000</v>
+        <v>-250133000</v>
       </c>
       <c r="AF2" t="n">
-        <v>392000</v>
+        <v>397000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-118167000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-939000</v>
-      </c>
+        <v>-35250000</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>119106000</v>
+        <v>35250000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>6285000</v>
+        <v>13082000</v>
       </c>
       <c r="AK2" t="n">
-        <v>326000</v>
+        <v>452000</v>
       </c>
       <c r="AL2" t="n">
-        <v>6611000</v>
+        <v>13534000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-89527000</v>
+        <v>-233586000</v>
       </c>
       <c r="AN2" t="n">
-        <v>126160000</v>
+        <v>251094000</v>
       </c>
       <c r="AO2" t="n">
-        <v>20195000</v>
+        <v>150442000</v>
       </c>
       <c r="AP2" t="n">
-        <v>105965000</v>
+        <v>102041000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>43610000</v>
+        <v>36403000</v>
       </c>
       <c r="AR2" t="n">
-        <v>62355000</v>
+        <v>65638000</v>
       </c>
       <c r="AS2" t="n">
-        <v>36633000</v>
+        <v>17508000</v>
       </c>
       <c r="AT2" t="n">
-        <v>405318000</v>
+        <v>502746000</v>
       </c>
       <c r="AU2" t="n">
-        <v>441951000</v>
+        <v>520254000</v>
       </c>
       <c r="AV2" t="n">
-        <v>441951000</v>
+        <v>520254000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>-2917.497157</v>
+        <v>-3340.457848</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001058</v>
+        <v>0.001027</v>
       </c>
       <c r="D3" t="n">
-        <v>-95121000</v>
+        <v>-163480000</v>
       </c>
       <c r="E3" t="n">
-        <v>-2758000</v>
+        <v>-3253000</v>
       </c>
       <c r="F3" t="n">
-        <v>-2758000</v>
+        <v>-3253000</v>
       </c>
       <c r="G3" t="n">
-        <v>-125596000</v>
+        <v>-216128000</v>
       </c>
       <c r="H3" t="n">
-        <v>27300000</v>
+        <v>42202000</v>
       </c>
       <c r="I3" t="n">
-        <v>409124000</v>
+        <v>481374000</v>
       </c>
       <c r="J3" t="n">
-        <v>-97879000</v>
+        <v>-166733000</v>
       </c>
       <c r="K3" t="n">
-        <v>-125179000</v>
+        <v>-208935000</v>
       </c>
       <c r="L3" t="n">
-        <v>6529000</v>
+        <v>6932000</v>
       </c>
       <c r="M3" t="n">
-        <v>550000</v>
+        <v>436000</v>
       </c>
       <c r="N3" t="n">
-        <v>7079000</v>
+        <v>7368000</v>
       </c>
       <c r="O3" t="n">
-        <v>-122840917.497157</v>
+        <v>-212878340.457848</v>
       </c>
       <c r="P3" t="n">
-        <v>-125596000</v>
+        <v>-216128000</v>
       </c>
       <c r="Q3" t="n">
-        <v>571664000</v>
+        <v>716790000</v>
       </c>
       <c r="R3" t="n">
-        <v>-125179000</v>
+        <v>-208935000</v>
       </c>
       <c r="S3" t="n">
-        <v>106529670</v>
+        <v>100026185</v>
       </c>
       <c r="T3" t="n">
-        <v>106529670</v>
+        <v>100026185</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.18</v>
+        <v>-2.2</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.18</v>
+        <v>-2.2</v>
       </c>
       <c r="W3" t="n">
-        <v>-125596000</v>
+        <v>-216128000</v>
       </c>
       <c r="X3" t="n">
-        <v>-125596000</v>
+        <v>-216128000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-125596000</v>
+        <v>-216128000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-6972000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-125596000</v>
+        <v>-209156000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-125596000</v>
+        <v>-209156000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-133000</v>
+        <v>-215000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-125729000</v>
+        <v>-209371000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1558000</v>
+        <v>2516000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-2758000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-46000</v>
-      </c>
+        <v>-3253000</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>2804000</v>
+        <v>3253000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>6529000</v>
+        <v>6932000</v>
       </c>
       <c r="AK3" t="n">
-        <v>550000</v>
+        <v>436000</v>
       </c>
       <c r="AL3" t="n">
-        <v>7079000</v>
+        <v>7368000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-131064000</v>
+        <v>-215572000</v>
       </c>
       <c r="AN3" t="n">
-        <v>162540000</v>
+        <v>235416000</v>
       </c>
       <c r="AO3" t="n">
-        <v>69113000</v>
+        <v>128998000</v>
       </c>
       <c r="AP3" t="n">
-        <v>94811000</v>
+        <v>106722000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>30532000</v>
+        <v>42321000</v>
       </c>
       <c r="AR3" t="n">
-        <v>64279000</v>
+        <v>64401000</v>
       </c>
       <c r="AS3" t="n">
-        <v>31476000</v>
+        <v>19844000</v>
       </c>
       <c r="AT3" t="n">
-        <v>409124000</v>
+        <v>481374000</v>
       </c>
       <c r="AU3" t="n">
-        <v>440600000</v>
+        <v>501218000</v>
       </c>
       <c r="AV3" t="n">
-        <v>440600000</v>
+        <v>501218000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>-3340.457848</v>
+        <v>-2917.497157</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001027</v>
+        <v>0.001058</v>
       </c>
       <c r="D4" t="n">
-        <v>-163480000</v>
+        <v>-95121000</v>
       </c>
       <c r="E4" t="n">
-        <v>-3253000</v>
+        <v>-2758000</v>
       </c>
       <c r="F4" t="n">
-        <v>-3253000</v>
+        <v>-2758000</v>
       </c>
       <c r="G4" t="n">
-        <v>-216128000</v>
+        <v>-125596000</v>
       </c>
       <c r="H4" t="n">
-        <v>42202000</v>
+        <v>27300000</v>
       </c>
       <c r="I4" t="n">
-        <v>481374000</v>
+        <v>409124000</v>
       </c>
       <c r="J4" t="n">
-        <v>-166733000</v>
+        <v>-97879000</v>
       </c>
       <c r="K4" t="n">
-        <v>-208935000</v>
+        <v>-125179000</v>
       </c>
       <c r="L4" t="n">
-        <v>6932000</v>
+        <v>6529000</v>
       </c>
       <c r="M4" t="n">
-        <v>436000</v>
+        <v>550000</v>
       </c>
       <c r="N4" t="n">
-        <v>7368000</v>
+        <v>7079000</v>
       </c>
       <c r="O4" t="n">
-        <v>-212878340.457848</v>
+        <v>-122840917.497157</v>
       </c>
       <c r="P4" t="n">
-        <v>-216128000</v>
+        <v>-125596000</v>
       </c>
       <c r="Q4" t="n">
-        <v>716790000</v>
+        <v>571664000</v>
       </c>
       <c r="R4" t="n">
-        <v>-208935000</v>
+        <v>-125179000</v>
       </c>
       <c r="S4" t="n">
-        <v>100026185</v>
+        <v>106529670</v>
       </c>
       <c r="T4" t="n">
-        <v>100026185</v>
+        <v>106529670</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.2</v>
+        <v>-1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.2</v>
+        <v>-1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>-216128000</v>
+        <v>-125596000</v>
       </c>
       <c r="X4" t="n">
-        <v>-216128000</v>
+        <v>-125596000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-216128000</v>
+        <v>-125596000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-6972000</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-209156000</v>
+        <v>-125596000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-209156000</v>
+        <v>-125596000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-215000</v>
+        <v>-133000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-209371000</v>
+        <v>-125729000</v>
       </c>
       <c r="AF4" t="n">
-        <v>2516000</v>
+        <v>1558000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-3253000</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>-2758000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-46000</v>
+      </c>
       <c r="AI4" t="n">
-        <v>3253000</v>
+        <v>2804000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>6932000</v>
+        <v>6529000</v>
       </c>
       <c r="AK4" t="n">
-        <v>436000</v>
+        <v>550000</v>
       </c>
       <c r="AL4" t="n">
-        <v>7368000</v>
+        <v>7079000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-215572000</v>
+        <v>-131064000</v>
       </c>
       <c r="AN4" t="n">
-        <v>235416000</v>
+        <v>162540000</v>
       </c>
       <c r="AO4" t="n">
-        <v>128998000</v>
+        <v>69113000</v>
       </c>
       <c r="AP4" t="n">
-        <v>106722000</v>
+        <v>94811000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>42321000</v>
+        <v>30532000</v>
       </c>
       <c r="AR4" t="n">
-        <v>64401000</v>
+        <v>64279000</v>
       </c>
       <c r="AS4" t="n">
-        <v>19844000</v>
+        <v>31476000</v>
       </c>
       <c r="AT4" t="n">
-        <v>481374000</v>
+        <v>409124000</v>
       </c>
       <c r="AU4" t="n">
-        <v>501218000</v>
+        <v>440600000</v>
       </c>
       <c r="AV4" t="n">
-        <v>501218000</v>
+        <v>440600000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>-410514.606229</v>
+        <v>-138913.202636</v>
       </c>
       <c r="C5" t="n">
-        <v>0.011646</v>
+        <v>0.00122</v>
       </c>
       <c r="D5" t="n">
-        <v>-161680000</v>
+        <v>-39890000</v>
       </c>
       <c r="E5" t="n">
-        <v>-35250000</v>
+        <v>-113844000</v>
       </c>
       <c r="F5" t="n">
-        <v>-35250000</v>
+        <v>-113844000</v>
       </c>
       <c r="G5" t="n">
-        <v>-247213000</v>
+        <v>-196448000</v>
       </c>
       <c r="H5" t="n">
-        <v>52751000</v>
+        <v>42628000</v>
       </c>
       <c r="I5" t="n">
-        <v>502746000</v>
+        <v>405318000</v>
       </c>
       <c r="J5" t="n">
-        <v>-196930000</v>
+        <v>-153734000</v>
       </c>
       <c r="K5" t="n">
-        <v>-249681000</v>
+        <v>-196362000</v>
       </c>
       <c r="L5" t="n">
-        <v>13082000</v>
+        <v>6285000</v>
       </c>
       <c r="M5" t="n">
-        <v>452000</v>
+        <v>326000</v>
       </c>
       <c r="N5" t="n">
-        <v>13534000</v>
+        <v>6611000</v>
       </c>
       <c r="O5" t="n">
-        <v>-212373514.606229</v>
+        <v>-82742913.202636</v>
       </c>
       <c r="P5" t="n">
-        <v>-247213000</v>
+        <v>-196448000</v>
       </c>
       <c r="Q5" t="n">
-        <v>753840000</v>
+        <v>531478000</v>
       </c>
       <c r="R5" t="n">
-        <v>-249681000</v>
+        <v>-196362000</v>
       </c>
       <c r="S5" t="n">
-        <v>93634809</v>
+        <v>112809468</v>
       </c>
       <c r="T5" t="n">
-        <v>93634809</v>
+        <v>112809468</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.6</v>
+        <v>-1.74</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.6</v>
+        <v>-1.74</v>
       </c>
       <c r="W5" t="n">
-        <v>-247213000</v>
+        <v>-196448000</v>
       </c>
       <c r="X5" t="n">
-        <v>-247213000</v>
+        <v>-196448000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-247213000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>7000</v>
-      </c>
+        <v>-196448000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>-247220000</v>
+        <v>-196448000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-247220000</v>
+        <v>-196448000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-2913000</v>
+        <v>-240000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-250133000</v>
+        <v>-196688000</v>
       </c>
       <c r="AF5" t="n">
-        <v>397000</v>
+        <v>392000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-35250000</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>-118167000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-939000</v>
+      </c>
       <c r="AI5" t="n">
-        <v>35250000</v>
+        <v>119106000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>13082000</v>
+        <v>6285000</v>
       </c>
       <c r="AK5" t="n">
-        <v>452000</v>
+        <v>326000</v>
       </c>
       <c r="AL5" t="n">
-        <v>13534000</v>
+        <v>6611000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-233586000</v>
+        <v>-89527000</v>
       </c>
       <c r="AN5" t="n">
-        <v>251094000</v>
+        <v>126160000</v>
       </c>
       <c r="AO5" t="n">
-        <v>150442000</v>
+        <v>20195000</v>
       </c>
       <c r="AP5" t="n">
-        <v>102041000</v>
+        <v>105965000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>36403000</v>
+        <v>43610000</v>
       </c>
       <c r="AR5" t="n">
-        <v>65638000</v>
+        <v>62355000</v>
       </c>
       <c r="AS5" t="n">
-        <v>17508000</v>
+        <v>36633000</v>
       </c>
       <c r="AT5" t="n">
-        <v>502746000</v>
+        <v>405318000</v>
       </c>
       <c r="AU5" t="n">
-        <v>520254000</v>
+        <v>441951000</v>
       </c>
       <c r="AV5" t="n">
-        <v>520254000</v>
+        <v>441951000</v>
       </c>
     </row>
   </sheetData>
@@ -1606,204 +1606,216 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>157605453</v>
+        <v>93634809</v>
       </c>
       <c r="C2" t="n">
-        <v>157605453</v>
+        <v>93634809</v>
       </c>
       <c r="D2" t="n">
-        <v>5997000</v>
+        <v>21207000</v>
       </c>
       <c r="E2" t="n">
-        <v>782961000</v>
+        <v>1247493000</v>
       </c>
       <c r="F2" t="n">
-        <v>787038000</v>
+        <v>1317469000</v>
       </c>
       <c r="G2" t="n">
-        <v>448543000</v>
+        <v>672161000</v>
       </c>
       <c r="H2" t="n">
-        <v>782961000</v>
+        <v>1247493000</v>
       </c>
       <c r="I2" t="n">
-        <v>5850000</v>
+        <v>5497000</v>
       </c>
       <c r="J2" t="n">
-        <v>786891000</v>
+        <v>1301759000</v>
       </c>
       <c r="K2" t="n">
-        <v>786891000</v>
+        <v>1301759000</v>
       </c>
       <c r="L2" t="n">
-        <v>786891000</v>
+        <v>1285864000</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-15895000</v>
       </c>
       <c r="N2" t="n">
-        <v>786891000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>15520000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-1720905000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2407435000</v>
-      </c>
+        <v>1301759000</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>1576000</v>
+        <v>187270000</v>
       </c>
       <c r="S2" t="n">
-        <v>1576000</v>
+        <v>187270000</v>
       </c>
       <c r="T2" t="n">
-        <v>82665000</v>
+        <v>121681000</v>
       </c>
       <c r="U2" t="n">
-        <v>16846000</v>
+        <v>14827000</v>
       </c>
       <c r="V2" t="n">
-        <v>11756000</v>
+        <v>11690000</v>
       </c>
       <c r="W2" t="n">
-        <v>5090000</v>
+        <v>3137000</v>
       </c>
       <c r="X2" t="n">
-        <v>5090000</v>
+        <v>3137000</v>
       </c>
       <c r="Y2" t="n">
-        <v>65819000</v>
+        <v>106854000</v>
       </c>
       <c r="Z2" t="n">
-        <v>907000</v>
+        <v>18070000</v>
       </c>
       <c r="AA2" t="n">
-        <v>760000</v>
+        <v>2360000</v>
       </c>
       <c r="AB2" t="n">
-        <v>147000</v>
+        <v>15710000</v>
       </c>
       <c r="AC2" t="n">
-        <v>55601000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
+        <v>71537000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
       <c r="AE2" t="n">
-        <v>55601000</v>
+        <v>71537000</v>
       </c>
       <c r="AF2" t="n">
-        <v>869556000</v>
+        <v>1407545000</v>
       </c>
       <c r="AG2" t="n">
-        <v>355194000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>628530000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>11661000</v>
+      </c>
       <c r="AI2" t="n">
         <v>205000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>9193000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>7861000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>108000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>69035000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
+        <v>110548000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>25562000</v>
+      </c>
       <c r="AN2" t="n">
-        <v>69035000</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
+        <v>84986000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>3930000</v>
+        <v>54266000</v>
       </c>
       <c r="AR2" t="n">
-        <v>3930000</v>
+        <v>43702000</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>10564000</v>
       </c>
       <c r="AT2" t="n">
-        <v>272831000</v>
+        <v>455650000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-686254000</v>
+        <v>-818949000</v>
       </c>
       <c r="AV2" t="n">
-        <v>959085000</v>
+        <v>1274599000</v>
       </c>
       <c r="AW2" t="n">
-        <v>14971000</v>
+        <v>73770000</v>
       </c>
       <c r="AX2" t="n">
         <v>130160000</v>
       </c>
       <c r="AY2" t="n">
-        <v>159266000</v>
+        <v>304904000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>118235000</v>
+        <v>151420000</v>
       </c>
       <c r="BA2" t="n">
-        <v>536453000</v>
+        <v>614345000</v>
       </c>
       <c r="BB2" t="n">
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>514362000</v>
+        <v>779015000</v>
       </c>
       <c r="BD2" t="n">
-        <v>12096000</v>
+        <v>18227000</v>
       </c>
       <c r="BE2" t="n">
-        <v>2265000</v>
-      </c>
-      <c r="BF2" t="inlineStr"/>
+        <v>21986000</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>123727000</v>
+      </c>
       <c r="BG2" t="n">
-        <v>97811000</v>
-      </c>
-      <c r="BH2" t="inlineStr"/>
+        <v>131580000</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>18227000</v>
+      </c>
       <c r="BI2" t="n">
-        <v>97459000</v>
+        <v>131255000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>352000</v>
+        <v>325000</v>
       </c>
       <c r="BK2" t="n">
-        <v>120651000</v>
-      </c>
-      <c r="BL2" t="inlineStr"/>
+        <v>123727000</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>394000</v>
+      </c>
       <c r="BM2" t="n">
-        <v>195343000</v>
+        <v>247627000</v>
       </c>
       <c r="BN2" t="n">
-        <v>-31671000</v>
+        <v>-75557000</v>
       </c>
       <c r="BO2" t="n">
-        <v>227014000</v>
+        <v>323184000</v>
       </c>
       <c r="BP2" t="n">
-        <v>86196000</v>
+        <v>235474000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3669000</v>
+        <v>12051000</v>
       </c>
       <c r="BR2" t="n">
-        <v>82527000</v>
+        <v>223423000</v>
       </c>
       <c r="BS2" t="n">
-        <v>82527000</v>
+        <v>223423000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
         <v>105070359</v>
@@ -1812,43 +1824,43 @@
         <v>105070359</v>
       </c>
       <c r="D3" t="n">
-        <v>17769000</v>
+        <v>23313000</v>
       </c>
       <c r="E3" t="n">
-        <v>969588000</v>
+        <v>1107908000</v>
       </c>
       <c r="F3" t="n">
-        <v>980530000</v>
+        <v>1120975000</v>
       </c>
       <c r="G3" t="n">
-        <v>506393000</v>
+        <v>672659000</v>
       </c>
       <c r="H3" t="n">
-        <v>969588000</v>
+        <v>1107908000</v>
       </c>
       <c r="I3" t="n">
-        <v>7309000</v>
+        <v>10728000</v>
       </c>
       <c r="J3" t="n">
-        <v>970070000</v>
+        <v>1108390000</v>
       </c>
       <c r="K3" t="n">
-        <v>970070000</v>
+        <v>1108390000</v>
       </c>
       <c r="L3" t="n">
-        <v>970070000</v>
+        <v>1108349000</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-41000</v>
       </c>
       <c r="N3" t="n">
-        <v>970070000</v>
+        <v>1108390000</v>
       </c>
       <c r="O3" t="n">
-        <v>17750000</v>
+        <v>18434000</v>
       </c>
       <c r="P3" t="n">
-        <v>-1733547000</v>
+        <v>-1521857000</v>
       </c>
       <c r="Q3" t="n">
         <v>2390451000</v>
@@ -1860,66 +1872,70 @@
         <v>210141000</v>
       </c>
       <c r="T3" t="n">
-        <v>103439000</v>
+        <v>116207000</v>
       </c>
       <c r="U3" t="n">
-        <v>18054000</v>
+        <v>21153000</v>
       </c>
       <c r="V3" t="n">
-        <v>12367000</v>
+        <v>13308000</v>
       </c>
       <c r="W3" t="n">
-        <v>5687000</v>
+        <v>7845000</v>
       </c>
       <c r="X3" t="n">
-        <v>5687000</v>
+        <v>7845000</v>
       </c>
       <c r="Y3" t="n">
-        <v>85385000</v>
+        <v>95054000</v>
       </c>
       <c r="Z3" t="n">
-        <v>12082000</v>
+        <v>15468000</v>
       </c>
       <c r="AA3" t="n">
-        <v>1622000</v>
+        <v>2883000</v>
       </c>
       <c r="AB3" t="n">
-        <v>10460000</v>
+        <v>12585000</v>
       </c>
       <c r="AC3" t="n">
-        <v>64106000</v>
+        <v>69470000</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>64106000</v>
+        <v>69470000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1073509000</v>
+        <v>1224556000</v>
       </c>
       <c r="AG3" t="n">
-        <v>481731000</v>
+        <v>456843000</v>
       </c>
       <c r="AH3" t="n">
-        <v>673000</v>
+        <v>205000</v>
       </c>
       <c r="AI3" t="n">
         <v>205000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8733000</v>
+        <v>8380000</v>
       </c>
       <c r="AK3" t="n">
-        <v>63612000</v>
+        <v>10030000</v>
       </c>
       <c r="AL3" t="n">
-        <v>63504000</v>
+        <v>9922000</v>
       </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>63504000</v>
-      </c>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
+        <v>9922000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ3" t="n">
         <v>482000</v>
       </c>
@@ -1930,81 +1946,85 @@
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>408807000</v>
+        <v>437854000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-574409000</v>
+        <v>-544036000</v>
       </c>
       <c r="AV3" t="n">
-        <v>983216000</v>
+        <v>981890000</v>
       </c>
       <c r="AW3" t="n">
-        <v>70767000</v>
+        <v>107986000</v>
       </c>
       <c r="AX3" t="n">
         <v>130160000</v>
       </c>
       <c r="AY3" t="n">
-        <v>159564000</v>
+        <v>135903000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>123737000</v>
+        <v>138656000</v>
       </c>
       <c r="BA3" t="n">
-        <v>498988000</v>
+        <v>469185000</v>
       </c>
       <c r="BB3" t="n">
         <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>591778000</v>
+        <v>767713000</v>
       </c>
       <c r="BD3" t="n">
-        <v>17878000</v>
+        <v>23626000</v>
       </c>
       <c r="BE3" t="n">
-        <v>19382000</v>
-      </c>
-      <c r="BF3" t="inlineStr"/>
+        <v>19882000</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>99465000</v>
+      </c>
       <c r="BG3" t="n">
-        <v>105317000</v>
+        <v>117842000</v>
       </c>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="n">
-        <v>104956000</v>
+        <v>117456000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>361000</v>
+        <v>386000</v>
       </c>
       <c r="BK3" t="n">
-        <v>120196000</v>
-      </c>
-      <c r="BL3" t="inlineStr"/>
+        <v>99465000</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0</v>
+      </c>
       <c r="BM3" t="n">
-        <v>202298000</v>
+        <v>253054000</v>
       </c>
       <c r="BN3" t="n">
-        <v>-25881000</v>
+        <v>-22403000</v>
       </c>
       <c r="BO3" t="n">
-        <v>228179000</v>
+        <v>275457000</v>
       </c>
       <c r="BP3" t="n">
-        <v>126707000</v>
+        <v>253844000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4877000</v>
+        <v>108188000</v>
       </c>
       <c r="BR3" t="n">
-        <v>121830000</v>
+        <v>145656000</v>
       </c>
       <c r="BS3" t="n">
-        <v>121830000</v>
+        <v>145656000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
         <v>105070359</v>
@@ -2013,43 +2033,43 @@
         <v>105070359</v>
       </c>
       <c r="D4" t="n">
-        <v>23313000</v>
+        <v>17769000</v>
       </c>
       <c r="E4" t="n">
-        <v>1107908000</v>
+        <v>969588000</v>
       </c>
       <c r="F4" t="n">
-        <v>1120975000</v>
+        <v>980530000</v>
       </c>
       <c r="G4" t="n">
-        <v>672659000</v>
+        <v>506393000</v>
       </c>
       <c r="H4" t="n">
-        <v>1107908000</v>
+        <v>969588000</v>
       </c>
       <c r="I4" t="n">
-        <v>10728000</v>
+        <v>7309000</v>
       </c>
       <c r="J4" t="n">
-        <v>1108390000</v>
+        <v>970070000</v>
       </c>
       <c r="K4" t="n">
-        <v>1108390000</v>
+        <v>970070000</v>
       </c>
       <c r="L4" t="n">
-        <v>1108349000</v>
+        <v>970070000</v>
       </c>
       <c r="M4" t="n">
-        <v>-41000</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1108390000</v>
+        <v>970070000</v>
       </c>
       <c r="O4" t="n">
-        <v>18434000</v>
+        <v>17750000</v>
       </c>
       <c r="P4" t="n">
-        <v>-1521857000</v>
+        <v>-1733547000</v>
       </c>
       <c r="Q4" t="n">
         <v>2390451000</v>
@@ -2061,70 +2081,66 @@
         <v>210141000</v>
       </c>
       <c r="T4" t="n">
-        <v>116207000</v>
+        <v>103439000</v>
       </c>
       <c r="U4" t="n">
-        <v>21153000</v>
+        <v>18054000</v>
       </c>
       <c r="V4" t="n">
-        <v>13308000</v>
+        <v>12367000</v>
       </c>
       <c r="W4" t="n">
-        <v>7845000</v>
+        <v>5687000</v>
       </c>
       <c r="X4" t="n">
-        <v>7845000</v>
+        <v>5687000</v>
       </c>
       <c r="Y4" t="n">
-        <v>95054000</v>
+        <v>85385000</v>
       </c>
       <c r="Z4" t="n">
-        <v>15468000</v>
+        <v>12082000</v>
       </c>
       <c r="AA4" t="n">
-        <v>2883000</v>
+        <v>1622000</v>
       </c>
       <c r="AB4" t="n">
-        <v>12585000</v>
+        <v>10460000</v>
       </c>
       <c r="AC4" t="n">
-        <v>69470000</v>
+        <v>64106000</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>69470000</v>
+        <v>64106000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1224556000</v>
+        <v>1073509000</v>
       </c>
       <c r="AG4" t="n">
-        <v>456843000</v>
+        <v>481731000</v>
       </c>
       <c r="AH4" t="n">
-        <v>205000</v>
+        <v>673000</v>
       </c>
       <c r="AI4" t="n">
         <v>205000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>8380000</v>
+        <v>8733000</v>
       </c>
       <c r="AK4" t="n">
-        <v>10030000</v>
+        <v>63612000</v>
       </c>
       <c r="AL4" t="n">
-        <v>9922000</v>
+        <v>63504000</v>
       </c>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>9922000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
+        <v>63504000</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
         <v>482000</v>
       </c>
@@ -2135,289 +2151,273 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>437854000</v>
+        <v>408807000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-544036000</v>
+        <v>-574409000</v>
       </c>
       <c r="AV4" t="n">
-        <v>981890000</v>
+        <v>983216000</v>
       </c>
       <c r="AW4" t="n">
-        <v>107986000</v>
+        <v>70767000</v>
       </c>
       <c r="AX4" t="n">
         <v>130160000</v>
       </c>
       <c r="AY4" t="n">
-        <v>135903000</v>
+        <v>159564000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>138656000</v>
+        <v>123737000</v>
       </c>
       <c r="BA4" t="n">
-        <v>469185000</v>
+        <v>498988000</v>
       </c>
       <c r="BB4" t="n">
         <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>767713000</v>
+        <v>591778000</v>
       </c>
       <c r="BD4" t="n">
-        <v>23626000</v>
+        <v>17878000</v>
       </c>
       <c r="BE4" t="n">
-        <v>19882000</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>99465000</v>
-      </c>
+        <v>19382000</v>
+      </c>
+      <c r="BF4" t="inlineStr"/>
       <c r="BG4" t="n">
-        <v>117842000</v>
+        <v>105317000</v>
       </c>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="n">
-        <v>117456000</v>
+        <v>104956000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>386000</v>
+        <v>361000</v>
       </c>
       <c r="BK4" t="n">
-        <v>99465000</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0</v>
-      </c>
+        <v>120196000</v>
+      </c>
+      <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="n">
-        <v>253054000</v>
+        <v>202298000</v>
       </c>
       <c r="BN4" t="n">
-        <v>-22403000</v>
+        <v>-25881000</v>
       </c>
       <c r="BO4" t="n">
-        <v>275457000</v>
+        <v>228179000</v>
       </c>
       <c r="BP4" t="n">
-        <v>253844000</v>
+        <v>126707000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>108188000</v>
+        <v>4877000</v>
       </c>
       <c r="BR4" t="n">
-        <v>145656000</v>
+        <v>121830000</v>
       </c>
       <c r="BS4" t="n">
-        <v>145656000</v>
+        <v>121830000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>93634809</v>
+        <v>157605453</v>
       </c>
       <c r="C5" t="n">
-        <v>93634809</v>
+        <v>157605453</v>
       </c>
       <c r="D5" t="n">
-        <v>21207000</v>
+        <v>5997000</v>
       </c>
       <c r="E5" t="n">
-        <v>1247493000</v>
+        <v>782961000</v>
       </c>
       <c r="F5" t="n">
-        <v>1317469000</v>
+        <v>787038000</v>
       </c>
       <c r="G5" t="n">
-        <v>672161000</v>
+        <v>448543000</v>
       </c>
       <c r="H5" t="n">
-        <v>1247493000</v>
+        <v>782961000</v>
       </c>
       <c r="I5" t="n">
-        <v>5497000</v>
+        <v>5850000</v>
       </c>
       <c r="J5" t="n">
-        <v>1301759000</v>
+        <v>786891000</v>
       </c>
       <c r="K5" t="n">
-        <v>1301759000</v>
+        <v>786891000</v>
       </c>
       <c r="L5" t="n">
-        <v>1285864000</v>
+        <v>786891000</v>
       </c>
       <c r="M5" t="n">
-        <v>-15895000</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1301759000</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+        <v>786891000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>15520000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-1720905000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2407435000</v>
+      </c>
       <c r="R5" t="n">
-        <v>187270000</v>
+        <v>1576000</v>
       </c>
       <c r="S5" t="n">
-        <v>187270000</v>
+        <v>1576000</v>
       </c>
       <c r="T5" t="n">
-        <v>121681000</v>
+        <v>82665000</v>
       </c>
       <c r="U5" t="n">
-        <v>14827000</v>
+        <v>16846000</v>
       </c>
       <c r="V5" t="n">
-        <v>11690000</v>
+        <v>11756000</v>
       </c>
       <c r="W5" t="n">
-        <v>3137000</v>
+        <v>5090000</v>
       </c>
       <c r="X5" t="n">
-        <v>3137000</v>
+        <v>5090000</v>
       </c>
       <c r="Y5" t="n">
-        <v>106854000</v>
+        <v>65819000</v>
       </c>
       <c r="Z5" t="n">
-        <v>18070000</v>
+        <v>907000</v>
       </c>
       <c r="AA5" t="n">
-        <v>2360000</v>
+        <v>760000</v>
       </c>
       <c r="AB5" t="n">
-        <v>15710000</v>
+        <v>147000</v>
       </c>
       <c r="AC5" t="n">
-        <v>71537000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
+        <v>55601000</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>71537000</v>
+        <v>55601000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1407545000</v>
+        <v>869556000</v>
       </c>
       <c r="AG5" t="n">
-        <v>628530000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>11661000</v>
-      </c>
+        <v>355194000</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
         <v>205000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>7861000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>108000</v>
-      </c>
+        <v>9193000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>110548000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>25562000</v>
-      </c>
+        <v>69035000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>84986000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
+        <v>69035000</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>54266000</v>
+        <v>3930000</v>
       </c>
       <c r="AR5" t="n">
-        <v>43702000</v>
+        <v>3930000</v>
       </c>
       <c r="AS5" t="n">
-        <v>10564000</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>455650000</v>
+        <v>272831000</v>
       </c>
       <c r="AU5" t="n">
-        <v>-818949000</v>
+        <v>-686254000</v>
       </c>
       <c r="AV5" t="n">
-        <v>1274599000</v>
+        <v>959085000</v>
       </c>
       <c r="AW5" t="n">
-        <v>73770000</v>
+        <v>14971000</v>
       </c>
       <c r="AX5" t="n">
         <v>130160000</v>
       </c>
       <c r="AY5" t="n">
-        <v>304904000</v>
+        <v>159266000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>151420000</v>
+        <v>118235000</v>
       </c>
       <c r="BA5" t="n">
-        <v>614345000</v>
+        <v>536453000</v>
       </c>
       <c r="BB5" t="n">
         <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>779015000</v>
+        <v>514362000</v>
       </c>
       <c r="BD5" t="n">
-        <v>18227000</v>
+        <v>12096000</v>
       </c>
       <c r="BE5" t="n">
-        <v>21986000</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>123727000</v>
-      </c>
+        <v>2265000</v>
+      </c>
+      <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
-        <v>131580000</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>18227000</v>
-      </c>
+        <v>97811000</v>
+      </c>
+      <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="n">
-        <v>131255000</v>
+        <v>97459000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>325000</v>
+        <v>352000</v>
       </c>
       <c r="BK5" t="n">
-        <v>123727000</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>394000</v>
-      </c>
+        <v>120651000</v>
+      </c>
+      <c r="BL5" t="inlineStr"/>
       <c r="BM5" t="n">
-        <v>247627000</v>
+        <v>195343000</v>
       </c>
       <c r="BN5" t="n">
-        <v>-75557000</v>
+        <v>-31671000</v>
       </c>
       <c r="BO5" t="n">
-        <v>323184000</v>
+        <v>227014000</v>
       </c>
       <c r="BP5" t="n">
-        <v>235474000</v>
+        <v>86196000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>12051000</v>
+        <v>3669000</v>
       </c>
       <c r="BR5" t="n">
-        <v>223423000</v>
+        <v>82527000</v>
       </c>
       <c r="BS5" t="n">
-        <v>223423000</v>
+        <v>82527000</v>
       </c>
     </row>
   </sheetData>
@@ -2668,552 +2668,552 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-58428000</v>
+        <v>-129710000</v>
       </c>
       <c r="C2" t="n">
-        <v>-15313000</v>
+        <v>-64000000</v>
       </c>
       <c r="D2" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>17509000</v>
-      </c>
+        <v>59286000</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>-36116000</v>
+        <v>-34545000</v>
       </c>
       <c r="G2" t="n">
-        <v>69137000</v>
+        <v>223423000</v>
       </c>
       <c r="H2" t="n">
-        <v>120889000</v>
+        <v>337430000</v>
       </c>
       <c r="I2" t="n">
-        <v>-344000</v>
+        <v>18496000</v>
       </c>
       <c r="J2" t="n">
-        <v>-51408000</v>
+        <v>-132503000</v>
       </c>
       <c r="K2" t="n">
-        <v>5897000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>17509000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>17509000</v>
-      </c>
+        <v>-7651000</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-10313000</v>
+        <v>-4714000</v>
       </c>
       <c r="O2" t="n">
-        <v>-10313000</v>
+        <v>-4714000</v>
       </c>
       <c r="P2" t="n">
-        <v>-15313000</v>
+        <v>-64000000</v>
       </c>
       <c r="Q2" t="n">
-        <v>5000000</v>
+        <v>59286000</v>
       </c>
       <c r="R2" t="n">
-        <v>-34993000</v>
+        <v>-29687000</v>
       </c>
       <c r="S2" t="n">
-        <v>10183000</v>
+        <v>-16672000</v>
       </c>
       <c r="T2" t="n">
-        <v>3359000</v>
+        <v>9626000</v>
       </c>
       <c r="U2" t="n">
-        <v>-12449000</v>
+        <v>11904000</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>11904000</v>
       </c>
       <c r="W2" t="n">
-        <v>-12449000</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
       <c r="AA2" t="n">
-        <v>-9282000</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-9282000</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-26814000</v>
+        <v>-34545000</v>
       </c>
       <c r="AD2" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-26834000</v>
+        <v>-34545000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-22312000</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+        <v>-95165000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-682000</v>
+      </c>
       <c r="AH2" t="n">
-        <v>-326000</v>
+        <v>-452000</v>
       </c>
       <c r="AI2" t="n">
-        <v>4426000</v>
+        <v>-107259000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>7402000</v>
+        <v>-8065000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-8391000</v>
+        <v>2727000</v>
       </c>
       <c r="AL2" t="n">
-        <v>7903000</v>
+        <v>-6727000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-2488000</v>
+        <v>-95194000</v>
       </c>
       <c r="AN2" t="n">
-        <v>13430000</v>
+        <v>25585000</v>
       </c>
       <c r="AO2" t="n">
-        <v>42628000</v>
+        <v>52751000</v>
       </c>
       <c r="AP2" t="n">
-        <v>5460000</v>
+        <v>21575000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>37168000</v>
+        <v>31176000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-4323000</v>
+        <v>46287000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-18000</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>-921000</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-196688000</v>
+        <v>-250133000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>-44918000</v>
+        <v>-74538000</v>
       </c>
       <c r="C3" t="n">
-        <v>-32125000</v>
+        <v>-27125000</v>
       </c>
       <c r="D3" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
+        <v>24000000</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>-38230000</v>
+        <v>-72953000</v>
       </c>
       <c r="G3" t="n">
-        <v>120889000</v>
+        <v>100434000</v>
       </c>
       <c r="H3" t="n">
-        <v>100434000</v>
+        <v>223423000</v>
       </c>
       <c r="I3" t="n">
-        <v>-7915000</v>
+        <v>-2050000</v>
       </c>
       <c r="J3" t="n">
-        <v>28370000</v>
+        <v>-120939000</v>
       </c>
       <c r="K3" t="n">
-        <v>-4409000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
+        <v>-5993000</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>-2125000</v>
+        <v>-3125000</v>
       </c>
       <c r="O3" t="n">
-        <v>-2125000</v>
+        <v>-3125000</v>
       </c>
       <c r="P3" t="n">
-        <v>-32125000</v>
+        <v>-27125000</v>
       </c>
       <c r="Q3" t="n">
-        <v>30000000</v>
+        <v>24000000</v>
       </c>
       <c r="R3" t="n">
-        <v>39467000</v>
+        <v>-113361000</v>
       </c>
       <c r="S3" t="n">
-        <v>3984000</v>
+        <v>929000</v>
       </c>
       <c r="T3" t="n">
-        <v>3750000</v>
+        <v>3886000</v>
       </c>
       <c r="U3" t="n">
-        <v>69781000</v>
+        <v>-45222000</v>
       </c>
       <c r="V3" t="n">
-        <v>69781000</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-45222000</v>
+      </c>
       <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
+        <v>-1000</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-22620000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-22620000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-38048000</v>
+        <v>-50333000</v>
       </c>
       <c r="AD3" t="n">
-        <v>182000</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-38230000</v>
+        <v>-50333000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-6688000</v>
+        <v>-1585000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>380000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-550000</v>
+        <v>-436000</v>
       </c>
       <c r="AI3" t="n">
-        <v>27616000</v>
+        <v>32177000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-3952000</v>
+        <v>8968000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-6217000</v>
+        <v>-7000</v>
       </c>
       <c r="AL3" t="n">
-        <v>9722000</v>
+        <v>14744000</v>
       </c>
       <c r="AM3" t="n">
-        <v>28063000</v>
+        <v>8472000</v>
       </c>
       <c r="AN3" t="n">
-        <v>35321000</v>
+        <v>24443000</v>
       </c>
       <c r="AO3" t="n">
-        <v>27300000</v>
+        <v>42202000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>15454000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>27300000</v>
+        <v>26748000</v>
       </c>
       <c r="AR3" t="n">
-        <v>26144000</v>
+        <v>17598000</v>
       </c>
       <c r="AS3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>47000</v>
+        <v>30000</v>
       </c>
       <c r="AU3" t="n">
-        <v>-125729000</v>
+        <v>-209371000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>-74538000</v>
+        <v>-44918000</v>
       </c>
       <c r="C4" t="n">
-        <v>-27125000</v>
+        <v>-32125000</v>
       </c>
       <c r="D4" t="n">
-        <v>24000000</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>30000000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
       <c r="F4" t="n">
-        <v>-72953000</v>
+        <v>-38230000</v>
       </c>
       <c r="G4" t="n">
+        <v>120889000</v>
+      </c>
+      <c r="H4" t="n">
         <v>100434000</v>
       </c>
-      <c r="H4" t="n">
-        <v>223423000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-2050000</v>
+        <v>-7915000</v>
       </c>
       <c r="J4" t="n">
-        <v>-120939000</v>
+        <v>28370000</v>
       </c>
       <c r="K4" t="n">
-        <v>-5993000</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+        <v>-4409000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
       <c r="N4" t="n">
-        <v>-3125000</v>
+        <v>-2125000</v>
       </c>
       <c r="O4" t="n">
-        <v>-3125000</v>
+        <v>-2125000</v>
       </c>
       <c r="P4" t="n">
-        <v>-27125000</v>
+        <v>-32125000</v>
       </c>
       <c r="Q4" t="n">
-        <v>24000000</v>
+        <v>30000000</v>
       </c>
       <c r="R4" t="n">
-        <v>-113361000</v>
+        <v>39467000</v>
       </c>
       <c r="S4" t="n">
-        <v>929000</v>
+        <v>3984000</v>
       </c>
       <c r="T4" t="n">
-        <v>3886000</v>
+        <v>3750000</v>
       </c>
       <c r="U4" t="n">
-        <v>-45222000</v>
+        <v>69781000</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-45222000</v>
-      </c>
+        <v>69781000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>-1000</v>
-      </c>
-      <c r="Y4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z4" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-22620000</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-22620000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-50333000</v>
+        <v>-38048000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>182000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-50333000</v>
+        <v>-38230000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1585000</v>
+        <v>-6688000</v>
       </c>
       <c r="AG4" t="n">
-        <v>380000</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-436000</v>
+        <v>-550000</v>
       </c>
       <c r="AI4" t="n">
-        <v>32177000</v>
+        <v>27616000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>8968000</v>
+        <v>-3952000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-7000</v>
+        <v>-6217000</v>
       </c>
       <c r="AL4" t="n">
-        <v>14744000</v>
+        <v>9722000</v>
       </c>
       <c r="AM4" t="n">
-        <v>8472000</v>
+        <v>28063000</v>
       </c>
       <c r="AN4" t="n">
-        <v>24443000</v>
+        <v>35321000</v>
       </c>
       <c r="AO4" t="n">
-        <v>42202000</v>
+        <v>27300000</v>
       </c>
       <c r="AP4" t="n">
-        <v>15454000</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>26748000</v>
+        <v>27300000</v>
       </c>
       <c r="AR4" t="n">
-        <v>17598000</v>
+        <v>26144000</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AT4" t="n">
-        <v>30000</v>
+        <v>47000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-209371000</v>
+        <v>-125729000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>-129710000</v>
+        <v>-58428000</v>
       </c>
       <c r="C5" t="n">
-        <v>-64000000</v>
+        <v>-15313000</v>
       </c>
       <c r="D5" t="n">
-        <v>59286000</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>5000000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>17509000</v>
+      </c>
       <c r="F5" t="n">
-        <v>-34545000</v>
+        <v>-36116000</v>
       </c>
       <c r="G5" t="n">
-        <v>223423000</v>
+        <v>69137000</v>
       </c>
       <c r="H5" t="n">
-        <v>337430000</v>
+        <v>120889000</v>
       </c>
       <c r="I5" t="n">
-        <v>18496000</v>
+        <v>-344000</v>
       </c>
       <c r="J5" t="n">
-        <v>-132503000</v>
+        <v>-51408000</v>
       </c>
       <c r="K5" t="n">
-        <v>-7651000</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+        <v>5897000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>17509000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>17509000</v>
+      </c>
       <c r="N5" t="n">
-        <v>-4714000</v>
+        <v>-10313000</v>
       </c>
       <c r="O5" t="n">
-        <v>-4714000</v>
+        <v>-10313000</v>
       </c>
       <c r="P5" t="n">
-        <v>-64000000</v>
+        <v>-15313000</v>
       </c>
       <c r="Q5" t="n">
-        <v>59286000</v>
+        <v>5000000</v>
       </c>
       <c r="R5" t="n">
-        <v>-29687000</v>
+        <v>-34993000</v>
       </c>
       <c r="S5" t="n">
-        <v>-16672000</v>
+        <v>10183000</v>
       </c>
       <c r="T5" t="n">
-        <v>9626000</v>
+        <v>3359000</v>
       </c>
       <c r="U5" t="n">
-        <v>11904000</v>
+        <v>-12449000</v>
       </c>
       <c r="V5" t="n">
-        <v>11904000</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-12449000</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>-9282000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-9282000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-34545000</v>
+        <v>-26814000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-34545000</v>
+        <v>-26834000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-95165000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-682000</v>
-      </c>
+        <v>-22312000</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>-452000</v>
+        <v>-326000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-107259000</v>
+        <v>4426000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-8065000</v>
+        <v>7402000</v>
       </c>
       <c r="AK5" t="n">
-        <v>2727000</v>
+        <v>-8391000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-6727000</v>
+        <v>7903000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-95194000</v>
+        <v>-2488000</v>
       </c>
       <c r="AN5" t="n">
-        <v>25585000</v>
+        <v>13430000</v>
       </c>
       <c r="AO5" t="n">
-        <v>52751000</v>
+        <v>42628000</v>
       </c>
       <c r="AP5" t="n">
-        <v>21575000</v>
+        <v>5460000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>31176000</v>
+        <v>37168000</v>
       </c>
       <c r="AR5" t="n">
-        <v>46287000</v>
+        <v>-4323000</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>-921000</v>
       </c>
       <c r="AU5" t="n">
-        <v>-250133000</v>
+        <v>-196688000</v>
       </c>
     </row>
   </sheetData>
@@ -3753,187 +3753,187 @@
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
           <t>longName</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>shortName</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -4036,28 +4036,28 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="W2" t="n">
         <v>0.28</v>
       </c>
-      <c r="V2" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.315</v>
-      </c>
       <c r="X2" t="n">
-        <v>0.315</v>
+        <v>0.3</v>
       </c>
       <c r="Y2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AA2" t="n">
         <v>0.28</v>
       </c>
-      <c r="Z2" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.315</v>
-      </c>
       <c r="AB2" t="n">
-        <v>0.315</v>
+        <v>0.3</v>
       </c>
       <c r="AC2" t="n">
         <v>1292889600</v>
@@ -4066,25 +4066,25 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.073</v>
+        <v>-0.004</v>
       </c>
       <c r="AF2" t="n">
-        <v>235055</v>
+        <v>331805</v>
       </c>
       <c r="AG2" t="n">
-        <v>235055</v>
+        <v>331805</v>
       </c>
       <c r="AH2" t="n">
-        <v>534781</v>
+        <v>136897</v>
       </c>
       <c r="AI2" t="n">
-        <v>8786</v>
+        <v>40350</v>
       </c>
       <c r="AJ2" t="n">
-        <v>8786</v>
+        <v>40350</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="AL2" t="n">
         <v>0.315</v>
@@ -4096,13 +4096,13 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>65901292</v>
+        <v>60671028</v>
       </c>
       <c r="AP2" t="n">
-        <v>58578926</v>
+        <v>62763135</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.155</v>
+        <v>0.166</v>
       </c>
       <c r="AR2" t="n">
         <v>0.7</v>
@@ -4114,13 +4114,13 @@
         <v>0.12</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.18937916</v>
+        <v>0.17434905</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.2815</v>
+        <v>0.2901</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.335315</v>
+        <v>0.33099</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -4137,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-69576704</v>
+        <v>-74806968</v>
       </c>
       <c r="BC2" t="n">
         <v>-0.57556</v>
@@ -4161,7 +4161,7 @@
         <v>2.676</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.117713</v>
+        <v>0.10837069</v>
       </c>
       <c r="BK2" t="n">
         <v>1751241600</v>
@@ -4187,16 +4187,16 @@
         <v>1703721600</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0.2</v>
+        <v>-0.215</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.9389999999999999</v>
+        <v>1.009</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.61849713</v>
+        <v>0.52284265</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BV2" t="n">
         <v>1.43332</v>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="BY2" t="n">
-        <v>0.315</v>
+        <v>0.29</v>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
@@ -4311,137 +4311,137 @@
       </c>
       <c r="DA2" t="inlineStr">
         <is>
+          <t>HENG TAI</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>-3.33334</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>finmb_5397526</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>136897</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0.74698794</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>0.166 - 0.7</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.5857143</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>52.284264</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1740737475</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1740737475</v>
+      </c>
+      <c r="DV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.000100016594</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.00034476593</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-0.040989995</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>-0.12384059</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>15</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EE2" t="n">
+        <v>1782097882</v>
+      </c>
+      <c r="EF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>1007343000000</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-0.01000002</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>0.28 - 0.3</t>
+        </is>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
           <t>Heng Tai Consumables Group Limited</t>
-        </is>
-      </c>
-      <c r="DB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>1007343000000</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>0.034999996</v>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>0.315 - 0.315</t>
-        </is>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DG2" t="n">
-        <v>534781</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>1.032258</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>0.155 - 0.7</t>
-        </is>
-      </c>
-      <c r="DK2" t="n">
-        <v>-0.385</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>61.849712</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>1780379689</v>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>finmb_5397526</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DX2" t="n">
-        <v>12.499998</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1740737475</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>1740737475</v>
-      </c>
-      <c r="EB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-1.11</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0.033499986</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0.11900527</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-0.020314991</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.0605848</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>HENG TAI</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr"/>
